--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2024.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:16</t>
+    <t xml:space="preserve">2026-09-09 21:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2024.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:00</t>
+    <t xml:space="preserve">2026-09-17 13:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2024.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:48</t>
+    <t xml:space="preserve">2026-10-05 18:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1503485.12</v>
+        <v>1503485.13</v>
       </c>
     </row>
     <row r="3">
@@ -546,7 +546,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1129161.62</v>
+        <v>1129161.63</v>
       </c>
     </row>
     <row r="10">
@@ -554,7 +554,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1088194.12</v>
+        <v>1088194.13</v>
       </c>
     </row>
     <row r="11">
@@ -578,7 +578,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1404446.12</v>
+        <v>1404446.13</v>
       </c>
     </row>
     <row r="14">
@@ -586,7 +586,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1099872.62</v>
+        <v>1099872.63</v>
       </c>
     </row>
     <row r="15">
